--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_06_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_06_20_Cau.xlsx
@@ -611,7 +611,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
@@ -625,7 +629,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Không dùng distance-only delta nếu working cost còn term downstream.</t>
+          <t>Các vị trí chèn khả thi có working-cost delta lần lượt là 12, 7, 9. Delta nhỏ nhất của cheapest feasible insertion là min(12, 7, 9) = 7.</t>
         </is>
       </c>
     </row>
@@ -739,7 +743,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
@@ -753,7 +761,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính chênh second-best trừ best cho từng order.</t>
+          <t>Regret = second-best insertion cost - best insertion cost. Order A: 9 - 4 = 5; Order B: 20 - 6 = 14; Order C: 11 - 5 = 6. Regret lớn nhất = max(5, 14, 6) = 14.</t>
         </is>
       </c>
     </row>
@@ -941,7 +949,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính load mỗi route sau swap, không chỉ tổng toàn fleet.</t>
+          <t>Đánh giá bước hoán đổi (swap): (a) Tải trọng mới của R1 là 10 - 8 + 2 = 4, của R2 là 6 - 2 + 8 = 12; (b) Lời giải bị vi phạm ràng buộc cứng (hard-invalid) vì R2 bị quá tải 2 đơn vị (12 &gt; capacity 10); (c) Mức giảm quãng đường không thể bù đắp vi phạm ràng buộc tải trọng cứng.</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1071,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>0.607</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
@@ -1077,7 +1089,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Move tốt hơn nhận trực tiếp; move xấu dùng exponent âm.</t>
+          <t>Xác suất chấp nhận move xấu trong Simulated Annealing: P = exp(-Δ / T) = exp(-5 / 10) = exp(-0,5) ≈ 0,60653..., làm tròn 3 chữ số là 0,607.</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1159,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
@@ -1161,7 +1177,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Trừ end-to-end reserve trước khi chia cho instance.</t>
+          <t>Tổng thời gian 30 phút, trừ thời gian dự phòng cố định (reserve) 6 phút, còn lại 30 - 6 = 24 phút. Chia đều cho 8 instances: 24 / 8 = 3 phút/instance.</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1195,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
@@ -1193,7 +1213,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Trừ mọi reserve end-to-end trước khi chia.</t>
+          <t>Tổng thời gian 42 phút. Tổng reserve: 7 phút cố định + 5 phút riêng cho instance cuối = 12 phút. Thời gian còn lại cho 4 instances đầu: 42 - 12 = 30 phút. Chia đều cho 4 instances: 30 / 4 = 7,5 phút/instance.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_06_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_06_20_Cau.xlsx
@@ -840,10 +840,31 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Phải so full delta của mọi alternative.
-Phân tích theo nguyên lý thiết kế: Phải so full delta của mọi alternative.</t>
+- 1.0 điểm: Tính chính xác chi phí phát sinh khi chèn vào route hiện tại: Delta = 10*1 + 6*3 = 28.
+- 1.0 điểm: Tính chính xác chi phí phạt nếu bỏ đơn X: Delta = 4 * 5 = 20.
+- 1.0 điểm: Ghi nhận chi phí phát sinh khi chèn vào route khác là 18 từ bối cảnh bài toán.
+- 1.0 điểm: So sánh đầy đủ 3 phương án (18 &lt; 20 &lt; 28) và kết luận chọn phương án chèn route khác là tối ưu nhất.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+So sánh Chi phí Vi phân (Delta Cost) giữa Chèn Route hiện tại, Route khác và Bỏ đơn:
+1. Thông số bài toán: Nhu cầu của X: demand(X) = 4. Trọng số làm việc: w_dist = 1, w_late = 3. Penalty bỏ đơn: p = 5.
+2. Tính toán Delta Cost cho từng phương án:
+- Phương án 1 (Chèn X vào Route hiện tại):
+  + Tăng cự ly: Delta_dist = 10.
+  + Tăng trễ hạn các trạm phía sau: Delta_late = 6.
+  + Chi phí phát sinh: Delta_C1 = 1 * Delta_dist + 3 * Delta_late = 1 * 10 + 3 * 6 = 10 + 18 = 28.
+- Phương án 2 (Chèn X vào Route khác):
+  + Theo dữ liệu đề bài, việc chèn vào route khác làm tăng chi phí toàn diện: Delta_C2 = 18.
+- Phương án 3 (Không phục vụ X - Unserved):
+  + Đơn hàng X bị bỏ lại với penalty p = 5 trên mỗi đơn vị nhu cầu.
+  + Chi phí phạt phát sinh: Delta_C3 = p * demand(X) = 5 * 4 = 20.
+3. So sánh Toàn diện và Quyết định:
+- Xếp hạng chi phí phát sinh: Delta_C2 (18) &lt; Delta_C3 (20) &lt; Delta_C1 (28).
+- Quyết định: Chọn Phương án 2 (Chèn X vào Route khác) là tối ưu nhất vì chi phí phát sinh 18 là thấp nhất.
+- Nhận xét đánh đổi: Nếu chỉ so giữa chèn route hiện tại (28) và bỏ đơn (20), ta sẽ nhầm lẫn chọn bỏ đơn. Nhưng khi so sánh toàn diện không gian phương án, chèn vào route khác mang lại hiệu quả vượt trội hơn cả.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Ra quyết định chèn điểm (insertion decision) trong heuristic tìm kiếm cục bộ đòi hỏi tính toán chi phí vi phân đầy đủ của mọi phương án khả dĩ (route hiện tại, các route khác, và phương án bỏ đơn chịu phạt) để tránh rơi vào tối ưu cục bộ kém.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Éric D. Taillard et al., 'A Tabu Search Heuristic for the Vehicle Routing Problem with Soft Time Windows', Transportation Science, 1997.</t>
         </is>
       </c>
     </row>
@@ -1388,10 +1409,32 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Dùng set difference required−submitted và submitted−required.
-Phân tích theo nguyên lý thiết kế: Dùng set difference required−submitted và submitted−required.</t>
+- 1.0 điểm: Phát hiện mâu thuẫn danh tính giữa tên tệp beta.json và tên đội đăng ký alpha trong JSON.
+- 1.0 điểm: Áp dụng chính xác phép trừ tập hợp S_required \ S_submitted để xác định instance thiếu là {i2}.
+- 1.0 điểm: Áp dụng chính xác phép trừ tập hợp S_submitted \ S_required để xác định instance thừa là {i4}.
+- 1.0 điểm: Nêu rõ 3 hành động khắc phục cụ thể (đổi tên file, bổ sung i2, xóa i4) trước khi submit chính thức.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Báo cáo Preflight Completeness và Team Identity Kiểm tra Trước khi Nộp bài:
+1. Kiểm tra Danh tính Đội (Team Identity Audit):
+- Tên đội đã đăng ký chính thức: `registered_team = 'alpha'`.
+- Tên đội khai báo bên trong JSON: `team = 'alpha'` -&gt; Trùng khớp hoàn toàn.
+- Tên tệp nộp bài: `filename = 'beta.json'`.
+- Chẩn đoán: Vi phạm quy chuẩn đặt tên tệp (Filename-Team Identity Mismatch). Tên tệp mang định danh 'beta' mâu thuẫn với tên đội 'alpha'. Nếu hệ thống chấm thi tự động sử dụng regex khớp tên file với registered team, bài nộp sẽ bị từ chối ngay lập tức. Cần đổi tên file thành `alpha.json`.
+2. Kiểm tra Tính Đầy đủ của Lời giải bằng Phép trừ Tập hợp (Set Difference Audit):
+- Tập instance yêu cầu: S_required = {i1, i2, i3}.
+- Tập instance có trong bài giải: S_submitted = {i1, i3, i4}.
+- Thiếu lời giải (Missing Instances): S_missing = S_required \ S_submitted = {i1, i2, i3} \ {i1, i3, i4} = {i2}.
+  =&gt; Instance `i2` chưa được giải quyết; bài nộp sẽ bị phạt điểm completeness hoặc đánh trượt instance này.
+- Lời giải dư thừa / không hợp lệ (Extraneous Instances): S_extraneous = S_submitted \ S_required = {i1, i3, i4} \ {i1, i2, i3} = {i4}.
+  =&gt; Instance `i4` không thuộc phạm vi đề bài yêu cầu, gây lãng phí tài nguyên và có thể kích hoạt lỗi validation schema lạ.
+3. Hành động khắc phục trước khi nộp (Corrective Actions):
+- Đổi tên file từ `beta.json` thành `alpha.json`.
+- Chạy bộ giải để bổ sung lời giải cho instance `i2`.
+- Loại bỏ key `i4` khỏi payload JSON nộp bài.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quy trình kiểm tra preflight trước khi nộp bài thi định tuyến sử dụng phép trừ tập hợp giữa danh sách instance yêu cầu và danh sách nộp để phát hiện chính xác instance thiếu hoặc thừa, đồng thời đối soát tính nhất quán giữa tên tệp và định danh đội.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Kenneth H. Rosen, 'Discrete Mathematics and Its Applications', McGraw-Hill, Chapter 2: Basic Structures: Sets, Functions, Sequences, Sums, and Matrices.</t>
         </is>
       </c>
     </row>
